--- a/outputs/q2/tables/Q2_第二检测点实验.xlsx
+++ b/outputs/q2/tables/Q2_第二检测点实验.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="候选点评分" sheetId="1" r:id="R01f1a72c107348f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="候选区域" sheetId="2" r:id="R9b81c1c8b7424d61"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="策略对比" sheetId="3" r:id="Ra50e27c485564784"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="权重敏感性" sheetId="4" r:id="R0d290e34f0564ce8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="闭环检验" sheetId="5" r:id="Rb6eae6739e974a4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="接收逻辑检验" sheetId="6" r:id="R2fcd0d86da3a4da4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="边界测试" sheetId="7" r:id="Rb494fba92dbe4cf8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="候选点评分" sheetId="1" r:id="R6f09b8806c914d6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="候选区域" sheetId="2" r:id="R572de12cbfa34623"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="策略对比" sheetId="3" r:id="Rc34768c230aa4c00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="权重敏感性" sheetId="4" r:id="Ra950904ba1014a66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="闭环检验" sheetId="5" r:id="Rd8b18563e9574bc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="接收逻辑检验" sheetId="6" r:id="Re655e76209c24ec0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="边界测试" sheetId="7" r:id="Rdc1e66f18db148be"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -22,7 +22,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="0.000"/>
   </x:numFmts>
-  <x:fonts count="5">
+  <x:fonts count="7">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -50,8 +50,20 @@
       <x:color rgb="FF1F2937"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF17365D"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF9C4A0B"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -61,6 +73,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3FB"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFCE4D6"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -84,9 +106,13 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="12">
+  <x:cellXfs count="18">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -103,6 +129,18 @@
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -425,741 +463,755 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="1" t="str">
+      <x:c r="A1" s="2" t="str">
         <x:v>问题2 第二检测点实验</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="2" t="str">
+      <x:c r="A2" s="4" t="str">
         <x:v>独立A1/A2物理域上的四指标归一化联合评分</x:v>
       </x:c>
     </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="3"/>
+      <x:c r="B3" s="3"/>
+      <x:c r="C3" s="3"/>
+      <x:c r="D3" s="3"/>
+      <x:c r="E3" s="3"/>
+      <x:c r="F3" s="3"/>
+      <x:c r="G3" s="3"/>
+      <x:c r="H3" s="3"/>
+      <x:c r="I3" s="3"/>
+      <x:c r="J3" s="3"/>
+      <x:c r="K3" s="3"/>
+      <x:c r="L3" s="3"/>
+    </x:row>
     <x:row r="4" ht="34" customHeight="1">
-      <x:c r="A4" s="8" t="str">
+      <x:c r="A4" s="10" t="str">
         <x:v>x_m</x:v>
       </x:c>
-      <x:c r="B4" s="8" t="str">
+      <x:c r="B4" s="10" t="str">
         <x:v>y_m</x:v>
       </x:c>
-      <x:c r="C4" s="8" t="str">
+      <x:c r="C4" s="10" t="str">
         <x:v>q_geo</x:v>
       </x:c>
-      <x:c r="D4" s="8" t="str">
+      <x:c r="D4" s="10" t="str">
         <x:v>p_rec</x:v>
       </x:c>
-      <x:c r="E4" s="8" t="str">
+      <x:c r="E4" s="10" t="str">
         <x:v>travel_s</x:v>
       </x:c>
-      <x:c r="F4" s="8" t="str">
+      <x:c r="F4" s="10" t="str">
         <x:v>r_pred_m</x:v>
       </x:c>
-      <x:c r="G4" s="8" t="str">
+      <x:c r="G4" s="10" t="str">
         <x:v>guaranteed_samples</x:v>
       </x:c>
-      <x:c r="H4" s="8" t="str">
+      <x:c r="H4" s="10" t="str">
         <x:v>q_geo_norm</x:v>
       </x:c>
-      <x:c r="I4" s="8" t="str">
+      <x:c r="I4" s="10" t="str">
         <x:v>p_rec_norm</x:v>
       </x:c>
-      <x:c r="J4" s="8" t="str">
+      <x:c r="J4" s="10" t="str">
         <x:v>travel_norm</x:v>
       </x:c>
-      <x:c r="K4" s="8" t="str">
+      <x:c r="K4" s="10" t="str">
         <x:v>r_pred_norm</x:v>
       </x:c>
-      <x:c r="L4" s="8" t="str">
+      <x:c r="L4" s="10" t="str">
         <x:v>score</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="11" t="n">
+      <x:c r="A5" s="15" t="n">
         <x:v>-51.459067209</x:v>
       </x:c>
-      <x:c r="B5" s="11" t="n">
+      <x:c r="B5" s="15" t="n">
         <x:v>-495.172615777</x:v>
       </x:c>
-      <x:c r="C5" s="11" t="n">
+      <x:c r="C5" s="15" t="n">
         <x:v>0.5350104065965057</x:v>
       </x:c>
-      <x:c r="D5" s="11" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
-      <x:c r="E5" s="11" t="n">
+      <x:c r="D5" s="15" t="n">
+        <x:v>0.6666666666666666</x:v>
+      </x:c>
+      <x:c r="E5" s="15" t="n">
         <x:v>140.00000000009385</x:v>
       </x:c>
-      <x:c r="F5" s="11" t="n">
+      <x:c r="F5" s="15" t="n">
         <x:v>31.87790451974684</x:v>
       </x:c>
-      <x:c r="G5" s="11" t="n">
+      <x:c r="G5" s="15" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H5" s="11" t="n">
+      <x:c r="H5" s="15" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I5" s="11" t="n">
+      <x:c r="I5" s="15" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J5" s="11" t="n">
+      <x:c r="J5" s="15" t="n">
         <x:v>0.9999999999999453</x:v>
       </x:c>
-      <x:c r="K5" s="11" t="n">
+      <x:c r="K5" s="15" t="n">
         <x:v>0.33456175128274057</x:v>
       </x:c>
-      <x:c r="L5" s="11" t="n">
+      <x:c r="L5" s="15" t="n">
         <x:v>0.43308764974346</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="11" t="n">
+      <x:c r="A6" s="15" t="n">
         <x:v>-826.814017764</x:v>
       </x:c>
-      <x:c r="B6" s="11" t="n">
+      <x:c r="B6" s="15" t="n">
         <x:v>245.772668819</x:v>
       </x:c>
-      <x:c r="C6" s="11" t="n">
+      <x:c r="C6" s="15" t="n">
         <x:v>0.5350104065963945</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="n">
+      <x:c r="D6" s="15" t="n">
+        <x:v>0.6666666666666666</x:v>
+      </x:c>
+      <x:c r="E6" s="15" t="n">
         <x:v>140.0000000000803</x:v>
       </x:c>
-      <x:c r="F6" s="11" t="n">
+      <x:c r="F6" s="15" t="n">
         <x:v>31.87790451975778</x:v>
       </x:c>
-      <x:c r="G6" s="11" t="n">
+      <x:c r="G6" s="15" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H6" s="11" t="n">
+      <x:c r="H6" s="15" t="n">
         <x:v>0.9999999999995386</x:v>
       </x:c>
-      <x:c r="I6" s="11" t="n">
+      <x:c r="I6" s="15" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="n">
+      <x:c r="J6" s="15" t="n">
         <x:v>0.9999999999996063</x:v>
       </x:c>
-      <x:c r="K6" s="11" t="n">
+      <x:c r="K6" s="15" t="n">
         <x:v>0.33456175128319343</x:v>
       </x:c>
-      <x:c r="L6" s="11" t="n">
+      <x:c r="L6" s="15" t="n">
         <x:v>0.43308764974325886</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="11" t="n">
+      <x:c r="A7" s="13" t="n">
         <x:v>-946.466696245</x:v>
       </x:c>
-      <x:c r="B7" s="11" t="n">
+      <x:c r="B7" s="13" t="n">
         <x:v>221.863704383</x:v>
       </x:c>
-      <x:c r="C7" s="11" t="n">
+      <x:c r="C7" s="13" t="n">
         <x:v>0.5082077987658759</x:v>
       </x:c>
-      <x:c r="D7" s="11" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="n">
+      <x:c r="D7" s="13" t="n">
+        <x:v>0.6666666666666666</x:v>
+      </x:c>
+      <x:c r="E7" s="13" t="n">
         <x:v>140.00000000009604</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="n">
+      <x:c r="F7" s="13" t="n">
         <x:v>35.373396888926614</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="n">
+      <x:c r="G7" s="13" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="n">
+      <x:c r="H7" s="13" t="n">
         <x:v>0.8887121305239648</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="n">
+      <x:c r="I7" s="13" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="n">
+      <x:c r="J7" s="13" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="n">
+      <x:c r="K7" s="13" t="n">
         <x:v>0.47924070642451055</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="n">
+      <x:c r="L7" s="13" t="n">
         <x:v>0.36520110439848547</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="11" t="n">
+      <x:c r="A8" s="13" t="n">
         <x:v>-69.915616002</x:v>
       </x:c>
-      <x:c r="B8" s="11" t="n">
+      <x:c r="B8" s="13" t="n">
         <x:v>-615.786702246</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="n">
+      <x:c r="C8" s="13" t="n">
         <x:v>0.50820779876521</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
-      <x:c r="E8" s="11" t="n">
+      <x:c r="D8" s="13" t="n">
+        <x:v>0.6666666666666666</x:v>
+      </x:c>
+      <x:c r="E8" s="13" t="n">
         <x:v>139.99999999993472</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="n">
+      <x:c r="F8" s="13" t="n">
         <x:v>35.37339688895191</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="n">
+      <x:c r="G8" s="13" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H8" s="11" t="n">
+      <x:c r="H8" s="13" t="n">
         <x:v>0.8887121305212003</x:v>
       </x:c>
-      <x:c r="I8" s="11" t="n">
+      <x:c r="I8" s="13" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="13" t="n">
         <x:v>0.999999999995967</x:v>
       </x:c>
-      <x:c r="K8" s="11" t="n">
+      <x:c r="K8" s="13" t="n">
         <x:v>0.4792407064255575</x:v>
       </x:c>
-      <x:c r="L8" s="11" t="n">
+      <x:c r="L8" s="13" t="n">
         <x:v>0.3652011043979136</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="11" t="n">
+      <x:c r="A9" s="13" t="n">
         <x:v>-815.840586655</x:v>
       </x:c>
-      <x:c r="B9" s="11" t="n">
+      <x:c r="B9" s="13" t="n">
         <x:v>146.376573273</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="n">
+      <x:c r="C9" s="13" t="n">
         <x:v>0.4334115578723186</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
-      <x:c r="E9" s="11" t="n">
+      <x:c r="D9" s="13" t="n">
+        <x:v>0.6666666666666666</x:v>
+      </x:c>
+      <x:c r="E9" s="13" t="n">
         <x:v>119.99999999998674</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="n">
+      <x:c r="F9" s="13" t="n">
         <x:v>37.27391872090544</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="n">
+      <x:c r="G9" s="13" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H9" s="11" t="n">
+      <x:c r="H9" s="13" t="n">
         <x:v>0.5781485336359123</x:v>
       </x:c>
-      <x:c r="I9" s="11" t="n">
+      <x:c r="I9" s="13" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="13" t="n">
         <x:v>0.49999999999876843</x:v>
       </x:c>
-      <x:c r="K9" s="11" t="n">
+      <x:c r="K9" s="13" t="n">
         <x:v>0.5579035910296172</x:v>
       </x:c>
-      <x:c r="L9" s="11" t="n">
+      <x:c r="L9" s="13" t="n">
         <x:v>0.3157712685668306</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="11" t="n">
+      <x:c r="A10" s="13" t="n">
         <x:v>-151.250629037</x:v>
       </x:c>
-      <x:c r="B10" s="11" t="n">
+      <x:c r="B10" s="13" t="n">
         <x:v>-488.719384952</x:v>
       </x:c>
-      <x:c r="C10" s="11" t="n">
+      <x:c r="C10" s="13" t="n">
         <x:v>0.43341155787209007</x:v>
       </x:c>
-      <x:c r="D10" s="11" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
-      <x:c r="E10" s="11" t="n">
+      <x:c r="D10" s="13" t="n">
+        <x:v>0.6666666666666666</x:v>
+      </x:c>
+      <x:c r="E10" s="13" t="n">
         <x:v>119.99999999994156</x:v>
       </x:c>
-      <x:c r="F10" s="11" t="n">
+      <x:c r="F10" s="13" t="n">
         <x:v>37.273918720917585</x:v>
       </x:c>
-      <x:c r="G10" s="11" t="n">
+      <x:c r="G10" s="13" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H10" s="11" t="n">
+      <x:c r="H10" s="13" t="n">
         <x:v>0.5781485336349633</x:v>
       </x:c>
-      <x:c r="I10" s="11" t="n">
+      <x:c r="I10" s="13" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J10" s="11" t="n">
+      <x:c r="J10" s="13" t="n">
         <x:v>0.49999999999763906</x:v>
       </x:c>
-      <x:c r="K10" s="11" t="n">
+      <x:c r="K10" s="13" t="n">
         <x:v>0.5579035910301198</x:v>
       </x:c>
-      <x:c r="L10" s="11" t="n">
+      <x:c r="L10" s="13" t="n">
         <x:v>0.31577126856656734</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="11" t="n">
+      <x:c r="A11" s="13" t="n">
         <x:v>-167.070528001</x:v>
       </x:c>
-      <x:c r="B11" s="11" t="n">
+      <x:c r="B11" s="13" t="n">
         <x:v>-592.102887639</x:v>
       </x:c>
-      <x:c r="C11" s="11" t="n">
+      <x:c r="C11" s="13" t="n">
         <x:v>0.4145524304509361</x:v>
       </x:c>
-      <x:c r="D11" s="11" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
-      <x:c r="E11" s="11" t="n">
+      <x:c r="D11" s="13" t="n">
+        <x:v>0.6666666666666666</x:v>
+      </x:c>
+      <x:c r="E11" s="13" t="n">
         <x:v>120.00000000006253</x:v>
       </x:c>
-      <x:c r="F11" s="11" t="n">
+      <x:c r="F11" s="13" t="n">
         <x:v>40.23296579335166</x:v>
       </x:c>
-      <x:c r="G11" s="11" t="n">
+      <x:c r="G11" s="13" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H11" s="11" t="n">
+      <x:c r="H11" s="13" t="n">
         <x:v>0.4998430148533613</x:v>
       </x:c>
-      <x:c r="I11" s="11" t="n">
+      <x:c r="I11" s="13" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J11" s="11" t="n">
+      <x:c r="J11" s="13" t="n">
         <x:v>0.5000000000006631</x:v>
       </x:c>
-      <x:c r="K11" s="11" t="n">
+      <x:c r="K11" s="13" t="n">
         <x:v>0.6803789946184081</x:v>
       </x:c>
-      <x:c r="L11" s="11" t="n">
+      <x:c r="L11" s="13" t="n">
         <x:v>0.2638692562748953</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="11" t="n">
+      <x:c r="A12" s="13" t="n">
         <x:v>-918.400025352</x:v>
       </x:c>
-      <x:c r="B12" s="11" t="n">
+      <x:c r="B12" s="13" t="n">
         <x:v>125.883175185</x:v>
       </x:c>
-      <x:c r="C12" s="11" t="n">
+      <x:c r="C12" s="13" t="n">
         <x:v>0.4145524304503851</x:v>
       </x:c>
-      <x:c r="D12" s="11" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
-      <x:c r="E12" s="11" t="n">
+      <x:c r="D12" s="13" t="n">
+        <x:v>0.6666666666666666</x:v>
+      </x:c>
+      <x:c r="E12" s="13" t="n">
         <x:v>119.99999999995194</x:v>
       </x:c>
-      <x:c r="F12" s="11" t="n">
+      <x:c r="F12" s="13" t="n">
         <x:v>40.23296579338631</x:v>
       </x:c>
-      <x:c r="G12" s="11" t="n">
+      <x:c r="G12" s="13" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H12" s="11" t="n">
+      <x:c r="H12" s="13" t="n">
         <x:v>0.4998430148510734</x:v>
       </x:c>
-      <x:c r="I12" s="11" t="n">
+      <x:c r="I12" s="13" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J12" s="11" t="n">
+      <x:c r="J12" s="13" t="n">
         <x:v>0.4999999999978984</x:v>
       </x:c>
-      <x:c r="K12" s="11" t="n">
+      <x:c r="K12" s="13" t="n">
         <x:v>0.6803789946198424</x:v>
       </x:c>
-      <x:c r="L12" s="11" t="n">
+      <x:c r="L12" s="13" t="n">
         <x:v>0.2638692562742224</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="11" t="n">
+      <x:c r="A13" s="13" t="n">
         <x:v>-804.867155546</x:v>
       </x:c>
-      <x:c r="B13" s="11" t="n">
+      <x:c r="B13" s="13" t="n">
         <x:v>46.980477728</x:v>
       </x:c>
-      <x:c r="C13" s="11" t="n">
+      <x:c r="C13" s="13" t="n">
         <x:v>0.3211496664186766</x:v>
       </x:c>
-      <x:c r="D13" s="11" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
-      <x:c r="E13" s="11" t="n">
+      <x:c r="D13" s="13" t="n">
+        <x:v>0.6666666666666666</x:v>
+      </x:c>
+      <x:c r="E13" s="13" t="n">
         <x:v>100.000000000092</x:v>
       </x:c>
-      <x:c r="F13" s="11" t="n">
+      <x:c r="F13" s="13" t="n">
         <x:v>45.915549431141535</x:v>
       </x:c>
-      <x:c r="G13" s="11" t="n">
+      <x:c r="G13" s="13" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H13" s="11" t="n">
+      <x:c r="H13" s="13" t="n">
         <x:v>0.1120227446017427</x:v>
       </x:c>
-      <x:c r="I13" s="11" t="n">
+      <x:c r="I13" s="13" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J13" s="11" t="n">
+      <x:c r="J13" s="13" t="n">
         <x:v>2.900790718731902e-12</x:v>
       </x:c>
-      <x:c r="K13" s="11" t="n">
+      <x:c r="K13" s="13" t="n">
         <x:v>0.9155819864687599</x:v>
       </x:c>
-      <x:c r="L13" s="11" t="n">
+      <x:c r="L13" s="13" t="n">
         <x:v>0.15609156331642285</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="11" t="n">
+      <x:c r="A14" s="13" t="n">
         <x:v>-251.042190864</x:v>
       </x:c>
-      <x:c r="B14" s="11" t="n">
+      <x:c r="B14" s="13" t="n">
         <x:v>-482.266154126</x:v>
       </x:c>
-      <x:c r="C14" s="11" t="n">
+      <x:c r="C14" s="13" t="n">
         <x:v>0.3211496664180179</x:v>
       </x:c>
-      <x:c r="D14" s="11" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
-      <x:c r="E14" s="11" t="n">
+      <x:c r="D14" s="13" t="n">
+        <x:v>0.6666666666666666</x:v>
+      </x:c>
+      <x:c r="E14" s="13" t="n">
         <x:v>99.99999999997597</x:v>
       </x:c>
-      <x:c r="F14" s="11" t="n">
+      <x:c r="F14" s="13" t="n">
         <x:v>45.915549431193426</x:v>
       </x:c>
-      <x:c r="G14" s="11" t="n">
+      <x:c r="G14" s="13" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H14" s="11" t="n">
+      <x:c r="H14" s="13" t="n">
         <x:v>0.11202274459900771</x:v>
       </x:c>
-      <x:c r="I14" s="11" t="n">
+      <x:c r="I14" s="13" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J14" s="11" t="n">
+      <x:c r="J14" s="13" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K14" s="11" t="n">
+      <x:c r="K14" s="13" t="n">
         <x:v>0.9155819864709077</x:v>
       </x:c>
-      <x:c r="L14" s="11" t="n">
+      <x:c r="L14" s="13" t="n">
         <x:v>0.15609156331547114</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="11" t="n">
+      <x:c r="A15" s="13" t="n">
         <x:v>-890.33335446</x:v>
       </x:c>
-      <x:c r="B15" s="11" t="n">
+      <x:c r="B15" s="13" t="n">
         <x:v>29.902645988</x:v>
       </x:c>
-      <x:c r="C15" s="11" t="n">
+      <x:c r="C15" s="13" t="n">
         <x:v>0.3133994461295659</x:v>
       </x:c>
-      <x:c r="D15" s="11" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
-      <x:c r="E15" s="11" t="n">
+      <x:c r="D15" s="13" t="n">
+        <x:v>0.6666666666666666</x:v>
+      </x:c>
+      <x:c r="E15" s="13" t="n">
         <x:v>100.00000000005593</x:v>
       </x:c>
-      <x:c r="F15" s="11" t="n">
+      <x:c r="F15" s="13" t="n">
         <x:v>47.955117119660656</x:v>
       </x:c>
-      <x:c r="G15" s="11" t="n">
+      <x:c r="G15" s="13" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H15" s="11" t="n">
+      <x:c r="H15" s="13" t="n">
         <x:v>0.07984283474388898</x:v>
       </x:c>
-      <x:c r="I15" s="11" t="n">
+      <x:c r="I15" s="13" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J15" s="11" t="n">
+      <x:c r="J15" s="13" t="n">
         <x:v>1.9991119870550413e-12</x:v>
       </x:c>
-      <x:c r="K15" s="11" t="n">
+      <x:c r="K15" s="13" t="n">
         <x:v>0.9999999999988833</x:v>
       </x:c>
-      <x:c r="L15" s="11" t="n">
+      <x:c r="L15" s="13" t="n">
         <x:v>0.12794499216028454</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="11" t="n">
+      <x:c r="A16" s="13" t="n">
         <x:v>-264.225440001</x:v>
       </x:c>
-      <x:c r="B16" s="11" t="n">
+      <x:c r="B16" s="13" t="n">
         <x:v>-568.419073033</x:v>
       </x:c>
-      <x:c r="C16" s="11" t="n">
+      <x:c r="C16" s="13" t="n">
         <x:v>0.3133994461293992</x:v>
       </x:c>
-      <x:c r="D16" s="11" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
-      <x:c r="E16" s="11" t="n">
+      <x:c r="D16" s="13" t="n">
+        <x:v>0.6666666666666666</x:v>
+      </x:c>
+      <x:c r="E16" s="13" t="n">
         <x:v>100.00000000004341</x:v>
       </x:c>
-      <x:c r="F16" s="11" t="n">
+      <x:c r="F16" s="13" t="n">
         <x:v>47.955117119687635</x:v>
       </x:c>
-      <x:c r="G16" s="11" t="n">
+      <x:c r="G16" s="13" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H16" s="11" t="n">
+      <x:c r="H16" s="13" t="n">
         <x:v>0.07984283474319682</x:v>
       </x:c>
-      <x:c r="I16" s="11" t="n">
+      <x:c r="I16" s="13" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J16" s="11" t="n">
+      <x:c r="J16" s="13" t="n">
         <x:v>1.6861179119536566e-12</x:v>
       </x:c>
-      <x:c r="K16" s="11" t="n">
+      <x:c r="K16" s="13" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L16" s="11" t="n">
+      <x:c r="L16" s="13" t="n">
         <x:v>0.12794499215986593</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="11" t="n">
+      <x:c r="A17" s="13" t="n">
         <x:v>-109.036184662</x:v>
       </x:c>
-      <x:c r="B17" s="11" t="n">
+      <x:c r="B17" s="13" t="n">
         <x:v>-731.363443659</x:v>
       </x:c>
-      <x:c r="C17" s="11" t="n">
+      <x:c r="C17" s="13" t="n">
         <x:v>0.4668689164342498</x:v>
       </x:c>
-      <x:c r="D17" s="11" t="n">
+      <x:c r="D17" s="13" t="n">
         <x:v>0.3333333333333333</x:v>
       </x:c>
-      <x:c r="E17" s="11" t="n">
+      <x:c r="E17" s="13" t="n">
         <x:v>140.00000000004246</x:v>
       </x:c>
-      <x:c r="F17" s="11" t="n">
+      <x:c r="F17" s="13" t="n">
         <x:v>23.794779731609566</x:v>
       </x:c>
-      <x:c r="G17" s="11" t="n">
+      <x:c r="G17" s="13" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H17" s="11" t="n">
+      <x:c r="H17" s="13" t="n">
         <x:v>0.7170677826948803</x:v>
       </x:c>
-      <x:c r="I17" s="11" t="n">
+      <x:c r="I17" s="13" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J17" s="11" t="n">
+      <x:c r="J17" s="13" t="n">
         <x:v>0.9999999999986606</x:v>
       </x:c>
-      <x:c r="K17" s="11" t="n">
+      <x:c r="K17" s="13" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L17" s="11" t="n">
+      <x:c r="L17" s="13" t="n">
         <x:v>0.10097372394340895</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="11" t="n">
+      <x:c r="A18" s="13" t="n">
         <x:v>-1060.149833577</x:v>
       </x:c>
-      <x:c r="B18" s="11" t="n">
+      <x:c r="B18" s="13" t="n">
         <x:v>177.540501268</x:v>
       </x:c>
-      <x:c r="C18" s="11" t="n">
+      <x:c r="C18" s="13" t="n">
         <x:v>0.4668689164336113</x:v>
       </x:c>
-      <x:c r="D18" s="11" t="n">
+      <x:c r="D18" s="13" t="n">
         <x:v>0.3333333333333333</x:v>
       </x:c>
-      <x:c r="E18" s="11" t="n">
+      <x:c r="E18" s="13" t="n">
         <x:v>139.99999999993338</x:v>
       </x:c>
-      <x:c r="F18" s="11" t="n">
+      <x:c r="F18" s="13" t="n">
         <x:v>23.794779731630854</x:v>
       </x:c>
-      <x:c r="G18" s="11" t="n">
+      <x:c r="G18" s="13" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H18" s="11" t="n">
+      <x:c r="H18" s="13" t="n">
         <x:v>0.7170677826922289</x:v>
       </x:c>
-      <x:c r="I18" s="11" t="n">
+      <x:c r="I18" s="13" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J18" s="11" t="n">
+      <x:c r="J18" s="13" t="n">
         <x:v>0.9999999999959336</x:v>
       </x:c>
-      <x:c r="K18" s="11" t="n">
+      <x:c r="K18" s="13" t="n">
         <x:v>8.811077437137574e-13</x:v>
       </x:c>
-      <x:c r="L18" s="11" t="n">
+      <x:c r="L18" s="13" t="n">
         <x:v>0.10097372394271387</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="11" t="n">
+      <x:c r="A19" s="13" t="n">
         <x:v>-200.602443996</x:v>
       </x:c>
-      <x:c r="B19" s="11" t="n">
+      <x:c r="B19" s="13" t="n">
         <x:v>-691.168665994</x:v>
       </x:c>
-      <x:c r="C19" s="11" t="n">
+      <x:c r="C19" s="13" t="n">
         <x:v>0.38334571501005826</x:v>
       </x:c>
-      <x:c r="D19" s="11" t="n">
+      <x:c r="D19" s="13" t="n">
         <x:v>0.3333333333333333</x:v>
       </x:c>
-      <x:c r="E19" s="11" t="n">
+      <x:c r="E19" s="13" t="n">
         <x:v>120.00000000008231</x:v>
       </x:c>
-      <x:c r="F19" s="11" t="n">
+      <x:c r="F19" s="13" t="n">
         <x:v>25.116451737579563</x:v>
       </x:c>
-      <x:c r="G19" s="11" t="n">
+      <x:c r="G19" s="13" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H19" s="11" t="n">
+      <x:c r="H19" s="13" t="n">
         <x:v>0.37026872504148167</x:v>
       </x:c>
-      <x:c r="I19" s="11" t="n">
+      <x:c r="I19" s="13" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J19" s="11" t="n">
+      <x:c r="J19" s="13" t="n">
         <x:v>0.5000000000011576</x:v>
       </x:c>
-      <x:c r="K19" s="11" t="n">
+      <x:c r="K19" s="13" t="n">
         <x:v>0.05470420320463642</x:v>
       </x:c>
-      <x:c r="L19" s="11" t="n">
+      <x:c r="L19" s="13" t="n">
         <x:v>0.043653213123417654</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="11" t="n">
+      <x:c r="A20" s="13" t="n">
         <x:v>-1015.842714495</x:v>
       </x:c>
-      <x:c r="B20" s="11" t="n">
+      <x:c r="B20" s="13" t="n">
         <x:v>87.89185823</x:v>
       </x:c>
-      <x:c r="C20" s="11" t="n">
+      <x:c r="C20" s="13" t="n">
         <x:v>0.3833457150097754</x:v>
       </x:c>
-      <x:c r="D20" s="11" t="n">
+      <x:c r="D20" s="13" t="n">
         <x:v>0.3333333333333333</x:v>
       </x:c>
-      <x:c r="E20" s="11" t="n">
+      <x:c r="E20" s="13" t="n">
         <x:v>120.00000000003209</x:v>
       </x:c>
-      <x:c r="F20" s="11" t="n">
+      <x:c r="F20" s="13" t="n">
         <x:v>25.116451737590918</x:v>
       </x:c>
-      <x:c r="G20" s="11" t="n">
+      <x:c r="G20" s="13" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H20" s="11" t="n">
+      <x:c r="H20" s="13" t="n">
         <x:v>0.37026872504030706</x:v>
       </x:c>
-      <x:c r="I20" s="11" t="n">
+      <x:c r="I20" s="13" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J20" s="11" t="n">
+      <x:c r="J20" s="13" t="n">
         <x:v>0.49999999999990213</x:v>
       </x:c>
-      <x:c r="K20" s="11" t="n">
+      <x:c r="K20" s="13" t="n">
         <x:v>0.054704203205106376</x:v>
       </x:c>
-      <x:c r="L20" s="11" t="n">
+      <x:c r="L20" s="13" t="n">
         <x:v>0.043653213123100866</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="11" t="n">
+      <x:c r="A21" s="13" t="n">
         <x:v>-971.535595412</x:v>
       </x:c>
-      <x:c r="B21" s="11" t="n">
+      <x:c r="B21" s="13" t="n">
         <x:v>-1.756784808</x:v>
       </x:c>
-      <x:c r="C21" s="11" t="n">
+      <x:c r="C21" s="13" t="n">
         <x:v>0.29417007101620046</x:v>
       </x:c>
-      <x:c r="D21" s="11" t="n">
+      <x:c r="D21" s="13" t="n">
         <x:v>0.3333333333333333</x:v>
       </x:c>
-      <x:c r="E21" s="11" t="n">
+      <x:c r="E21" s="13" t="n">
         <x:v>100.00000000004219</x:v>
       </x:c>
-      <x:c r="F21" s="11" t="n">
+      <x:c r="F21" s="13" t="n">
         <x:v>27.681820514205153</x:v>
       </x:c>
-      <x:c r="G21" s="11" t="n">
+      <x:c r="G21" s="13" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H21" s="11" t="n">
+      <x:c r="H21" s="13" t="n">
         <x:v>1.608816208715674e-13</x:v>
       </x:c>
-      <x:c r="I21" s="11" t="n">
+      <x:c r="I21" s="13" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J21" s="11" t="n">
+      <x:c r="J21" s="13" t="n">
         <x:v>1.6555645743160639e-12</x:v>
       </x:c>
-      <x:c r="K21" s="11" t="n">
+      <x:c r="K21" s="13" t="n">
         <x:v>0.16088520289098485</x:v>
       </x:c>
-      <x:c r="L21" s="11" t="n">
+      <x:c r="L21" s="13" t="n">
         <x:v>-0.032177040578389</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="11" t="n">
+      <x:c r="A22" s="13" t="n">
         <x:v>-292.16870333</x:v>
       </x:c>
-      <x:c r="B22" s="11" t="n">
+      <x:c r="B22" s="13" t="n">
         <x:v>-650.973888328</x:v>
       </x:c>
-      <x:c r="C22" s="11" t="n">
+      <x:c r="C22" s="13" t="n">
         <x:v>0.2941700710161617</x:v>
       </x:c>
-      <x:c r="D22" s="11" t="n">
+      <x:c r="D22" s="13" t="n">
         <x:v>0.3333333333333333</x:v>
       </x:c>
-      <x:c r="E22" s="11" t="n">
+      <x:c r="E22" s="13" t="n">
         <x:v>100.0000000000418</x:v>
       </x:c>
-      <x:c r="F22" s="11" t="n">
+      <x:c r="F22" s="13" t="n">
         <x:v>27.68182051421091</x:v>
       </x:c>
-      <x:c r="G22" s="11" t="n">
+      <x:c r="G22" s="13" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H22" s="11" t="n">
+      <x:c r="H22" s="13" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I22" s="11" t="n">
+      <x:c r="I22" s="13" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J22" s="11" t="n">
+      <x:c r="J22" s="13" t="n">
         <x:v>1.6456169760154523e-12</x:v>
       </x:c>
-      <x:c r="K22" s="11" t="n">
+      <x:c r="K22" s="13" t="n">
         <x:v>0.16088520289122307</x:v>
       </x:c>
-      <x:c r="L22" s="11" t="n">
+      <x:c r="L22" s="13" t="n">
         <x:v>-0.03217704057849146</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43ef9c41428e4a8b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90c7c04ce6af4d39"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1167,7 +1219,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
-    <x:tabColor rgb="FF5B9BD5"/>
+    <x:tabColor rgb="FF1F5A94"/>
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -1181,88 +1233,97 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="1" t="str">
+      <x:c r="A1" s="2" t="str">
         <x:v>问题2 第二检测点实验</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="2" t="str">
+      <x:c r="A2" s="4" t="str">
         <x:v>评分达到峰值90%以上的第二检测点区域及执行点</x:v>
       </x:c>
     </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="3"/>
+      <x:c r="B3" s="3"/>
+      <x:c r="C3" s="3"/>
+      <x:c r="D3" s="3"/>
+      <x:c r="E3" s="3"/>
+      <x:c r="F3" s="3"/>
+      <x:c r="G3" s="3"/>
+    </x:row>
     <x:row r="4" ht="34" customHeight="1">
-      <x:c r="A4" s="8" t="str">
+      <x:c r="A4" s="10" t="str">
         <x:v>eta</x:v>
       </x:c>
-      <x:c r="B4" s="8" t="str">
+      <x:c r="B4" s="10" t="str">
         <x:v>评分阈值</x:v>
       </x:c>
-      <x:c r="C4" s="8" t="str">
+      <x:c r="C4" s="10" t="str">
         <x:v>x(m)</x:v>
       </x:c>
-      <x:c r="D4" s="8" t="str">
+      <x:c r="D4" s="10" t="str">
         <x:v>y(m)</x:v>
       </x:c>
-      <x:c r="E4" s="8" t="str">
+      <x:c r="E4" s="10" t="str">
         <x:v>评分</x:v>
       </x:c>
-      <x:c r="F4" s="8" t="str">
+      <x:c r="F4" s="10" t="str">
         <x:v>移动时间(s)</x:v>
       </x:c>
-      <x:c r="G4" s="8" t="str">
+      <x:c r="G4" s="10" t="str">
         <x:v>是否执行点</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="11" t="n">
+      <x:c r="A5" s="13" t="n">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="B5" s="11" t="n">
+      <x:c r="B5" s="13" t="n">
         <x:v>0.389778884769114</x:v>
       </x:c>
-      <x:c r="C5" s="11" t="n">
+      <x:c r="C5" s="13" t="n">
         <x:v>-826.814017764</x:v>
       </x:c>
-      <x:c r="D5" s="11" t="n">
+      <x:c r="D5" s="13" t="n">
         <x:v>245.772668819</x:v>
       </x:c>
-      <x:c r="E5" s="11" t="n">
+      <x:c r="E5" s="13" t="n">
         <x:v>0.43308764974325886</x:v>
       </x:c>
-      <x:c r="F5" s="11" t="n">
+      <x:c r="F5" s="13" t="n">
         <x:v>140.0000000000803</x:v>
       </x:c>
-      <x:c r="G5" s="11" t="str">
+      <x:c r="G5" s="13" t="str">
         <x:v>否</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="11" t="n">
+      <x:c r="A6" s="17" t="n">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="B6" s="11" t="n">
+      <x:c r="B6" s="17" t="n">
         <x:v>0.389778884769114</x:v>
       </x:c>
-      <x:c r="C6" s="11" t="n">
+      <x:c r="C6" s="17" t="n">
         <x:v>-51.459067209</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="n">
+      <x:c r="D6" s="17" t="n">
         <x:v>-495.172615777</x:v>
       </x:c>
-      <x:c r="E6" s="11" t="n">
+      <x:c r="E6" s="17" t="n">
         <x:v>0.43308764974346</x:v>
       </x:c>
-      <x:c r="F6" s="11" t="n">
+      <x:c r="F6" s="17" t="n">
         <x:v>140.00000000009385</x:v>
       </x:c>
-      <x:c r="G6" s="11" t="str">
+      <x:c r="G6" s="17" t="str">
         <x:v>是</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2da1eb2115934710"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90deec051ccd45a8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1270,7 +1331,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
-    <x:tabColor rgb="FF5B9BD5"/>
+    <x:tabColor rgb="FF7F9DB9"/>
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -1284,134 +1345,143 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="1" t="str">
+      <x:c r="A1" s="2" t="str">
         <x:v>问题2 第二检测点实验</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="2" t="str">
+      <x:c r="A2" s="4" t="str">
         <x:v>联合、仅几何、最近点与随机点的样本回放比较</x:v>
       </x:c>
     </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="3"/>
+      <x:c r="B3" s="3"/>
+      <x:c r="C3" s="3"/>
+      <x:c r="D3" s="3"/>
+      <x:c r="E3" s="3"/>
+      <x:c r="F3" s="3"/>
+      <x:c r="G3" s="3"/>
+    </x:row>
     <x:row r="4" ht="34" customHeight="1">
-      <x:c r="A4" s="8" t="str">
+      <x:c r="A4" s="10" t="str">
         <x:v>策略</x:v>
       </x:c>
-      <x:c r="B4" s="8" t="str">
+      <x:c r="B4" s="10" t="str">
         <x:v>S2_x(m)</x:v>
       </x:c>
-      <x:c r="C4" s="8" t="str">
+      <x:c r="C4" s="10" t="str">
         <x:v>S2_y(m)</x:v>
       </x:c>
-      <x:c r="D4" s="8" t="str">
+      <x:c r="D4" s="10" t="str">
         <x:v>保证接收比例</x:v>
       </x:c>
-      <x:c r="E4" s="8" t="str">
+      <x:c r="E4" s="10" t="str">
         <x:v>预测MEC(m)</x:v>
       </x:c>
-      <x:c r="F4" s="8" t="str">
+      <x:c r="F4" s="10" t="str">
         <x:v>移动时间(s)</x:v>
       </x:c>
-      <x:c r="G4" s="8" t="str">
+      <x:c r="G4" s="10" t="str">
         <x:v>综合评分</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="11" t="str">
+      <x:c r="A5" s="13" t="str">
         <x:v>四指标联合</x:v>
       </x:c>
-      <x:c r="B5" s="11" t="n">
+      <x:c r="B5" s="13" t="n">
         <x:v>-51.459067209</x:v>
       </x:c>
-      <x:c r="C5" s="11" t="n">
+      <x:c r="C5" s="13" t="n">
         <x:v>-495.172615777</x:v>
       </x:c>
-      <x:c r="D5" s="11" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
-      <x:c r="E5" s="11" t="n">
+      <x:c r="D5" s="13" t="n">
+        <x:v>0.6666666666666666</x:v>
+      </x:c>
+      <x:c r="E5" s="13" t="n">
         <x:v>31.87790451974684</x:v>
       </x:c>
-      <x:c r="F5" s="11" t="n">
+      <x:c r="F5" s="13" t="n">
         <x:v>140.00000000009385</x:v>
       </x:c>
-      <x:c r="G5" s="11" t="n">
+      <x:c r="G5" s="13" t="n">
         <x:v>0.43308764974346</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="11" t="str">
+      <x:c r="A6" s="13" t="str">
         <x:v>仅最大几何</x:v>
       </x:c>
-      <x:c r="B6" s="11" t="n">
+      <x:c r="B6" s="13" t="n">
         <x:v>-51.459067209</x:v>
       </x:c>
-      <x:c r="C6" s="11" t="n">
+      <x:c r="C6" s="13" t="n">
         <x:v>-495.172615777</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="n">
+      <x:c r="D6" s="13" t="n">
+        <x:v>0.6666666666666666</x:v>
+      </x:c>
+      <x:c r="E6" s="13" t="n">
         <x:v>31.87790451974684</x:v>
       </x:c>
-      <x:c r="F6" s="11" t="n">
+      <x:c r="F6" s="13" t="n">
         <x:v>140.00000000009385</x:v>
       </x:c>
-      <x:c r="G6" s="11" t="n">
+      <x:c r="G6" s="13" t="n">
         <x:v>0.43308764974346</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="11" t="str">
+      <x:c r="A7" s="13" t="str">
         <x:v>最近候选点</x:v>
       </x:c>
-      <x:c r="B7" s="11" t="n">
+      <x:c r="B7" s="13" t="n">
         <x:v>-251.042190864</x:v>
       </x:c>
-      <x:c r="C7" s="11" t="n">
+      <x:c r="C7" s="13" t="n">
         <x:v>-482.266154126</x:v>
       </x:c>
-      <x:c r="D7" s="11" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="n">
+      <x:c r="D7" s="13" t="n">
+        <x:v>0.6666666666666666</x:v>
+      </x:c>
+      <x:c r="E7" s="13" t="n">
         <x:v>45.915549431193426</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="n">
+      <x:c r="F7" s="13" t="n">
         <x:v>99.99999999997597</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="n">
+      <x:c r="G7" s="13" t="n">
         <x:v>0.15609156331547114</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="11" t="str">
+      <x:c r="A8" s="13" t="str">
         <x:v>随机候选点</x:v>
       </x:c>
-      <x:c r="B8" s="11" t="n">
+      <x:c r="B8" s="13" t="n">
         <x:v>-69.915616002</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="n">
+      <x:c r="C8" s="13" t="n">
         <x:v>-615.786702246</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
-      <x:c r="E8" s="11" t="n">
+      <x:c r="D8" s="13" t="n">
+        <x:v>0.6666666666666666</x:v>
+      </x:c>
+      <x:c r="E8" s="13" t="n">
         <x:v>35.37339688895191</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="n">
+      <x:c r="F8" s="13" t="n">
         <x:v>139.99999999993472</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="n">
+      <x:c r="G8" s="13" t="n">
         <x:v>0.3652011043979136</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0025ce1e8934b55"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1774bd589d6f4a83"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1419,7 +1489,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
-    <x:tabColor rgb="FF5B9BD5"/>
+    <x:tabColor rgb="FF7F9DB9"/>
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -1433,226 +1503,235 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="1" t="str">
+      <x:c r="A1" s="2" t="str">
         <x:v>问题2 第二检测点实验</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="2" t="str">
+      <x:c r="A2" s="4" t="str">
         <x:v>各权重±10%扰动后的最优点稳定性</x:v>
       </x:c>
     </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="3"/>
+      <x:c r="B3" s="3"/>
+      <x:c r="C3" s="3"/>
+      <x:c r="D3" s="3"/>
+      <x:c r="E3" s="3"/>
+      <x:c r="F3" s="3"/>
+      <x:c r="G3" s="3"/>
+    </x:row>
     <x:row r="4" ht="34" customHeight="1">
-      <x:c r="A4" s="8" t="str">
+      <x:c r="A4" s="10" t="str">
         <x:v>扰动参数</x:v>
       </x:c>
-      <x:c r="B4" s="8" t="str">
+      <x:c r="B4" s="10" t="str">
         <x:v>倍率</x:v>
       </x:c>
-      <x:c r="C4" s="8" t="str">
+      <x:c r="C4" s="10" t="str">
         <x:v>最优S2_x(m)</x:v>
       </x:c>
-      <x:c r="D4" s="8" t="str">
+      <x:c r="D4" s="10" t="str">
         <x:v>最优S2_y(m)</x:v>
       </x:c>
-      <x:c r="E4" s="8" t="str">
+      <x:c r="E4" s="10" t="str">
         <x:v>评分</x:v>
       </x:c>
-      <x:c r="F4" s="8" t="str">
+      <x:c r="F4" s="10" t="str">
         <x:v>保证接收比例</x:v>
       </x:c>
-      <x:c r="G4" s="8" t="str">
+      <x:c r="G4" s="10" t="str">
         <x:v>预测MEC(m)</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="11" t="str">
+      <x:c r="A5" s="13" t="str">
         <x:v>w1几何</x:v>
       </x:c>
-      <x:c r="B5" s="11" t="n">
+      <x:c r="B5" s="13" t="n">
         <x:v>0.9</x:v>
       </x:c>
-      <x:c r="C5" s="11" t="n">
+      <x:c r="C5" s="13" t="n">
         <x:v>-51.459067209</x:v>
       </x:c>
-      <x:c r="D5" s="11" t="n">
+      <x:c r="D5" s="13" t="n">
         <x:v>-495.172615777</x:v>
       </x:c>
-      <x:c r="E5" s="11" t="n">
+      <x:c r="E5" s="13" t="n">
         <x:v>0.39808764974346006</x:v>
       </x:c>
-      <x:c r="F5" s="11" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
-      <x:c r="G5" s="11" t="n">
+      <x:c r="F5" s="13" t="n">
+        <x:v>0.6666666666666666</x:v>
+      </x:c>
+      <x:c r="G5" s="13" t="n">
         <x:v>31.87790451974684</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="11" t="str">
+      <x:c r="A6" s="13" t="str">
         <x:v>w1几何</x:v>
       </x:c>
-      <x:c r="B6" s="11" t="n">
+      <x:c r="B6" s="13" t="n">
         <x:v>1.1</x:v>
       </x:c>
-      <x:c r="C6" s="11" t="n">
+      <x:c r="C6" s="13" t="n">
         <x:v>-51.459067209</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="n">
+      <x:c r="D6" s="13" t="n">
         <x:v>-495.172615777</x:v>
       </x:c>
-      <x:c r="E6" s="11" t="n">
+      <x:c r="E6" s="13" t="n">
         <x:v>0.4680876497434601</x:v>
       </x:c>
-      <x:c r="F6" s="11" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="n">
+      <x:c r="F6" s="13" t="n">
+        <x:v>0.6666666666666666</x:v>
+      </x:c>
+      <x:c r="G6" s="13" t="n">
         <x:v>31.87790451974684</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="11" t="str">
+      <x:c r="A7" s="13" t="str">
         <x:v>w2接收</x:v>
       </x:c>
-      <x:c r="B7" s="11" t="n">
+      <x:c r="B7" s="13" t="n">
         <x:v>0.9</x:v>
       </x:c>
-      <x:c r="C7" s="11" t="n">
+      <x:c r="C7" s="13" t="n">
         <x:v>-51.459067209</x:v>
       </x:c>
-      <x:c r="D7" s="11" t="n">
+      <x:c r="D7" s="13" t="n">
         <x:v>-495.172615777</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="n">
+      <x:c r="E7" s="13" t="n">
         <x:v>0.40308764974346006</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="n">
+      <x:c r="F7" s="13" t="n">
+        <x:v>0.6666666666666666</x:v>
+      </x:c>
+      <x:c r="G7" s="13" t="n">
         <x:v>31.87790451974684</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="11" t="str">
+      <x:c r="A8" s="13" t="str">
         <x:v>w2接收</x:v>
       </x:c>
-      <x:c r="B8" s="11" t="n">
+      <x:c r="B8" s="13" t="n">
         <x:v>1.1</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="n">
+      <x:c r="C8" s="13" t="n">
         <x:v>-51.459067209</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="n">
+      <x:c r="D8" s="13" t="n">
         <x:v>-495.172615777</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="n">
+      <x:c r="E8" s="13" t="n">
         <x:v>0.46308764974346</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
-      <x:c r="G8" s="11" t="n">
+      <x:c r="F8" s="13" t="n">
+        <x:v>0.6666666666666666</x:v>
+      </x:c>
+      <x:c r="G8" s="13" t="n">
         <x:v>31.87790451974684</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="11" t="str">
+      <x:c r="A9" s="13" t="str">
         <x:v>w3时间</x:v>
       </x:c>
-      <x:c r="B9" s="11" t="n">
+      <x:c r="B9" s="13" t="n">
         <x:v>0.9</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="n">
+      <x:c r="C9" s="13" t="n">
         <x:v>-51.459067209</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="n">
+      <x:c r="D9" s="13" t="n">
         <x:v>-495.172615777</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="n">
+      <x:c r="E9" s="13" t="n">
         <x:v>0.4480876497434591</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
-      <x:c r="G9" s="11" t="n">
+      <x:c r="F9" s="13" t="n">
+        <x:v>0.6666666666666666</x:v>
+      </x:c>
+      <x:c r="G9" s="13" t="n">
         <x:v>31.87790451974684</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="11" t="str">
+      <x:c r="A10" s="13" t="str">
         <x:v>w3时间</x:v>
       </x:c>
-      <x:c r="B10" s="11" t="n">
+      <x:c r="B10" s="13" t="n">
         <x:v>1.1</x:v>
       </x:c>
-      <x:c r="C10" s="11" t="n">
+      <x:c r="C10" s="13" t="n">
         <x:v>-51.459067209</x:v>
       </x:c>
-      <x:c r="D10" s="11" t="n">
+      <x:c r="D10" s="13" t="n">
         <x:v>-495.172615777</x:v>
       </x:c>
-      <x:c r="E10" s="11" t="n">
+      <x:c r="E10" s="13" t="n">
         <x:v>0.4180876497434608</x:v>
       </x:c>
-      <x:c r="F10" s="11" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
-      <x:c r="G10" s="11" t="n">
+      <x:c r="F10" s="13" t="n">
+        <x:v>0.6666666666666666</x:v>
+      </x:c>
+      <x:c r="G10" s="13" t="n">
         <x:v>31.87790451974684</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="11" t="str">
+      <x:c r="A11" s="13" t="str">
         <x:v>w4预测半径</x:v>
       </x:c>
-      <x:c r="B11" s="11" t="n">
+      <x:c r="B11" s="13" t="n">
         <x:v>0.9</x:v>
       </x:c>
-      <x:c r="C11" s="11" t="n">
+      <x:c r="C11" s="13" t="n">
         <x:v>-51.459067209</x:v>
       </x:c>
-      <x:c r="D11" s="11" t="n">
+      <x:c r="D11" s="13" t="n">
         <x:v>-495.172615777</x:v>
       </x:c>
-      <x:c r="E11" s="11" t="n">
+      <x:c r="E11" s="13" t="n">
         <x:v>0.4397788847691148</x:v>
       </x:c>
-      <x:c r="F11" s="11" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
-      <x:c r="G11" s="11" t="n">
+      <x:c r="F11" s="13" t="n">
+        <x:v>0.6666666666666666</x:v>
+      </x:c>
+      <x:c r="G11" s="13" t="n">
         <x:v>31.87790451974684</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="11" t="str">
+      <x:c r="A12" s="13" t="str">
         <x:v>w4预测半径</x:v>
       </x:c>
-      <x:c r="B12" s="11" t="n">
+      <x:c r="B12" s="13" t="n">
         <x:v>1.1</x:v>
       </x:c>
-      <x:c r="C12" s="11" t="n">
+      <x:c r="C12" s="13" t="n">
         <x:v>-51.459067209</x:v>
       </x:c>
-      <x:c r="D12" s="11" t="n">
+      <x:c r="D12" s="13" t="n">
         <x:v>-495.172615777</x:v>
       </x:c>
-      <x:c r="E12" s="11" t="n">
+      <x:c r="E12" s="13" t="n">
         <x:v>0.42639641471780515</x:v>
       </x:c>
-      <x:c r="F12" s="11" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
-      <x:c r="G12" s="11" t="n">
+      <x:c r="F12" s="13" t="n">
+        <x:v>0.6666666666666666</x:v>
+      </x:c>
+      <x:c r="G12" s="13" t="n">
         <x:v>31.87790451974684</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5cdc5657ecea4b5c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc00a1ebbe97846f4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1660,7 +1739,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
-    <x:tabColor rgb="FF5B9BD5"/>
+    <x:tabColor rgb="FF7F9DB9"/>
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -1669,67 +1748,71 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="1" t="str">
+      <x:c r="A1" s="2" t="str">
         <x:v>问题2 第二检测点实验</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="2" t="str">
+      <x:c r="A2" s="4" t="str">
         <x:v>no_signal 的1000m保证接收圆盘排除检验</x:v>
       </x:c>
     </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="3"/>
+      <x:c r="B3" s="3"/>
+    </x:row>
     <x:row r="4" ht="34" customHeight="1">
-      <x:c r="A4" s="8" t="str">
+      <x:c r="A4" s="10" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B4" s="8" t="str">
+      <x:c r="B4" s="10" t="str">
         <x:v>数值</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="11" t="str">
+      <x:c r="A5" s="13" t="str">
         <x:v>A1样本数</x:v>
       </x:c>
-      <x:c r="B5" s="11" t="n">
+      <x:c r="B5" s="13" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="11" t="str">
+      <x:c r="A6" s="13" t="str">
         <x:v>no_signal后保留样本数</x:v>
       </x:c>
-      <x:c r="B6" s="11" t="n">
+      <x:c r="B6" s="13" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="11" t="str">
+      <x:c r="A7" s="13" t="str">
         <x:v>1000m内被排除数</x:v>
       </x:c>
-      <x:c r="B7" s="11" t="n">
+      <x:c r="B7" s="13" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="11" t="str">
+      <x:c r="A8" s="13" t="str">
         <x:v>最优点预测MEC(m)</x:v>
       </x:c>
-      <x:c r="B8" s="11" t="n">
+      <x:c r="B8" s="13" t="n">
         <x:v>31.87790451974684</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="11" t="str">
+      <x:c r="A9" s="13" t="str">
         <x:v>最优点移动时间(s)</x:v>
       </x:c>
-      <x:c r="B9" s="11" t="n">
+      <x:c r="B9" s="13" t="n">
         <x:v>140.00000000009385</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra071beb785c94903"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2aadbc4830054569"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1737,7 +1820,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
-    <x:tabColor rgb="FF5B9BD5"/>
+    <x:tabColor rgb="FF7F9DB9"/>
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -1748,75 +1831,81 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="1" t="str">
+      <x:c r="A1" s="2" t="str">
         <x:v>问题2 第二检测点实验</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="2" t="str">
+      <x:c r="A2" s="4" t="str">
         <x:v>接收半径1000--1500m的蒙特卡洛逻辑核验</x:v>
       </x:c>
     </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="3"/>
+      <x:c r="B3" s="3"/>
+      <x:c r="C3" s="3"/>
+      <x:c r="D3" s="3"/>
+    </x:row>
     <x:row r="4" ht="34" customHeight="1">
-      <x:c r="A4" s="8" t="str">
+      <x:c r="A4" s="10" t="str">
         <x:v>测试距离(m)</x:v>
       </x:c>
-      <x:c r="B4" s="8" t="str">
+      <x:c r="B4" s="10" t="str">
         <x:v>接收率</x:v>
       </x:c>
-      <x:c r="C4" s="8" t="str">
+      <x:c r="C4" s="10" t="str">
         <x:v>no_signal率</x:v>
       </x:c>
-      <x:c r="D4" s="8" t="str">
+      <x:c r="D4" s="10" t="str">
         <x:v>no_signal约束解释</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="11" t="n">
+      <x:c r="A5" s="13" t="n">
         <x:v>900</x:v>
       </x:c>
-      <x:c r="B5" s="11" t="n">
+      <x:c r="B5" s="13" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="11" t="n">
+      <x:c r="C5" s="13" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D5" s="11" t="str">
+      <x:c r="D5" s="13" t="str">
         <x:v>确定排除</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="11" t="n">
+      <x:c r="A6" s="13" t="n">
         <x:v>1200</x:v>
       </x:c>
-      <x:c r="B6" s="11" t="n">
+      <x:c r="B6" s="13" t="n">
         <x:v>0.6045</x:v>
       </x:c>
-      <x:c r="C6" s="11" t="n">
+      <x:c r="C6" s="13" t="n">
         <x:v>0.39549999999999996</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="str">
+      <x:c r="D6" s="13" t="str">
         <x:v>不得硬删除</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="11" t="n">
+      <x:c r="A7" s="13" t="n">
         <x:v>1600</x:v>
       </x:c>
-      <x:c r="B7" s="11" t="n">
+      <x:c r="B7" s="13" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C7" s="11" t="n">
+      <x:c r="C7" s="13" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D7" s="11" t="str">
+      <x:c r="D7" s="13" t="str">
         <x:v>不得硬删除</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R106d916ee5f8467f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5583fd94cb84d21"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1824,7 +1913,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
-    <x:tabColor rgb="FF5B9BD5"/>
+    <x:tabColor rgb="FF7F9DB9"/>
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -1836,104 +1925,111 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="1" t="str">
+      <x:c r="A1" s="2" t="str">
         <x:v>问题2 第二检测点实验</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="2" t="str">
+      <x:c r="A2" s="4" t="str">
         <x:v>极端角度、退化几何与物理候选域的边界验证</x:v>
       </x:c>
     </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="3"/>
+      <x:c r="B3" s="3"/>
+      <x:c r="C3" s="3"/>
+      <x:c r="D3" s="3"/>
+      <x:c r="E3" s="3"/>
+    </x:row>
     <x:row r="4" ht="34" customHeight="1">
-      <x:c r="A4" s="8" t="str">
+      <x:c r="A4" s="10" t="str">
         <x:v>测试情况</x:v>
       </x:c>
-      <x:c r="B4" s="8" t="str">
+      <x:c r="B4" s="10" t="str">
         <x:v>区域状态</x:v>
       </x:c>
-      <x:c r="C4" s="8" t="str">
+      <x:c r="C4" s="10" t="str">
         <x:v>区域直径(m)</x:v>
       </x:c>
-      <x:c r="D4" s="8" t="str">
+      <x:c r="D4" s="10" t="str">
         <x:v>物理候选域MEC半径(m)</x:v>
       </x:c>
-      <x:c r="E4" s="8" t="str">
+      <x:c r="E4" s="10" t="str">
         <x:v>决策分支</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="11" t="str">
+      <x:c r="A5" s="13" t="str">
         <x:v>近似平行交会</x:v>
       </x:c>
-      <x:c r="B5" s="11" t="str">
+      <x:c r="B5" s="13" t="str">
         <x:v>polygon</x:v>
       </x:c>
-      <x:c r="C5" s="11" t="n">
+      <x:c r="C5" s="13" t="n">
         <x:v>1400.493351776162</x:v>
       </x:c>
-      <x:c r="D5" s="11" t="n">
+      <x:c r="D5" s="13" t="n">
         <x:v>700.2711620028005</x:v>
       </x:c>
-      <x:c r="E5" s="11" t="str">
+      <x:c r="E5" s="13" t="str">
         <x:v>继续检测</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="11" t="str">
+      <x:c r="A6" s="13" t="str">
         <x:v>圆域近边界</x:v>
       </x:c>
-      <x:c r="B6" s="11" t="str">
+      <x:c r="B6" s="13" t="str">
         <x:v>polygon</x:v>
       </x:c>
-      <x:c r="C6" s="11" t="n">
+      <x:c r="C6" s="13" t="n">
         <x:v>43.668533195641736</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="n">
+      <x:c r="D6" s="13" t="n">
         <x:v>21.834266597820868</x:v>
       </x:c>
-      <x:c r="E6" s="11" t="str">
+      <x:c r="E6" s="13" t="str">
         <x:v>继续检测</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="11" t="str">
+      <x:c r="A7" s="13" t="str">
         <x:v>可清除阈值示例</x:v>
       </x:c>
-      <x:c r="B7" s="11" t="str">
+      <x:c r="B7" s="13" t="str">
         <x:v>polygon</x:v>
       </x:c>
-      <x:c r="C7" s="11" t="n">
+      <x:c r="C7" s="13" t="n">
         <x:v>27.936615593398244</x:v>
       </x:c>
-      <x:c r="D7" s="11" t="n">
+      <x:c r="D7" s="13" t="n">
         <x:v>13.968307796698413</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="str">
+      <x:c r="E7" s="13" t="str">
         <x:v>清除</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="11" t="str">
+      <x:c r="A8" s="13" t="str">
         <x:v>需继续检测示例</x:v>
       </x:c>
-      <x:c r="B8" s="11" t="str">
+      <x:c r="B8" s="13" t="str">
         <x:v>polygon</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="n">
+      <x:c r="C8" s="13" t="n">
         <x:v>224.96840612844096</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="n">
+      <x:c r="D8" s="13" t="n">
         <x:v>112.48420306422048</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="str">
+      <x:c r="E8" s="13" t="str">
         <x:v>继续检测</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e8d9ce8a192458d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R861ef99d14704f45"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/q2/tables/Q2_第二检测点实验.xlsx
+++ b/outputs/q2/tables/Q2_第二检测点实验.xlsx
@@ -2,13 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="候选点评分" sheetId="1" r:id="R6f09b8806c914d6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="候选区域" sheetId="2" r:id="R572de12cbfa34623"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="策略对比" sheetId="3" r:id="Rc34768c230aa4c00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="权重敏感性" sheetId="4" r:id="Ra950904ba1014a66"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="闭环检验" sheetId="5" r:id="Rd8b18563e9574bc7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="接收逻辑检验" sheetId="6" r:id="Re655e76209c24ec0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="边界测试" sheetId="7" r:id="Rdc1e66f18db148be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="候选点评分" sheetId="1" r:id="R14b79c19c4f34bea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="候选区域" sheetId="2" r:id="Rb41f3955954646de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="策略对比" sheetId="3" r:id="R8821c237e756489f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="权重敏感性" sheetId="4" r:id="R6a6cf9302c954dec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="闭环检验" sheetId="5" r:id="R5589789f50f44a7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="接收逻辑检验" sheetId="6" r:id="Rd04834c4e46a484b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="边界测试" sheetId="7" r:id="Rea2ba2ac52fc4eef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="正式权重校准" sheetId="8" r:id="R5daeccfb835440b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="正式策略对比" sheetId="9" r:id="R237f84367c26417f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="正式权重鲁棒性" sheetId="10" r:id="R0df14054a4094c6b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -170,6 +173,21 @@
 </x:table>
 </file>
 
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Q2Table10" displayName="Q2Table10" ref="A4:G12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="7">
+    <x:tableColumn id="1" name="扰动"/>
+    <x:tableColumn id="2" name="倍率"/>
+    <x:tableColumn id="3" name="归一化权重"/>
+    <x:tableColumn id="4" name="接收率变化"/>
+    <x:tableColumn id="5" name="成功率变化"/>
+    <x:tableColumn id="6" name="MEC均值变化(m)"/>
+    <x:tableColumn id="7" name="时间均值变化(s)"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Q2Table2" displayName="Q2Table2" ref="A4:G6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
@@ -245,6 +263,42 @@
     <x:tableColumn id="3" name="区域直径(m)"/>
     <x:tableColumn id="4" name="物理候选域MEC半径(m)"/>
     <x:tableColumn id="5" name="决策分支"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Q2Table8" displayName="Q2Table8" ref="A4:L39" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="12">
+    <x:tableColumn id="1" name="权重w1几何"/>
+    <x:tableColumn id="2" name="权重w2接收"/>
+    <x:tableColumn id="3" name="权重w3时间"/>
+    <x:tableColumn id="4" name="权重w4预测"/>
+    <x:tableColumn id="5" name="外层损失L"/>
+    <x:tableColumn id="6" name="接收率"/>
+    <x:tableColumn id="7" name="MEC均值(m)"/>
+    <x:tableColumn id="8" name="MEC中位数(m)"/>
+    <x:tableColumn id="9" name="MEC_P90(m)"/>
+    <x:tableColumn id="10" name="≤20m成功率"/>
+    <x:tableColumn id="11" name="总时间均值(s)"/>
+    <x:tableColumn id="12" name="总时间P90(s)"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Q2Table9" displayName="Q2Table9" ref="A4:H8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="8">
+    <x:tableColumn id="1" name="策略"/>
+    <x:tableColumn id="2" name="接收率"/>
+    <x:tableColumn id="3" name="MEC均值(m)"/>
+    <x:tableColumn id="4" name="MEC中位数(m)"/>
+    <x:tableColumn id="5" name="MEC_P90(m)"/>
+    <x:tableColumn id="6" name="≤20m成功率"/>
+    <x:tableColumn id="7" name="总时间均值(s)"/>
+    <x:tableColumn id="8" name="总时间P90(s)"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -1211,7 +1265,257 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90c7c04ce6af4d39"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9599145c60648b5"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF7F9DB9"/>
+  </x:sheetPr>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="13" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14.800000190734863" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>问题2 第二检测点实验</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="4" t="str">
+        <x:v>权重±10%并重新归一化后的完整重搜回放</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="3"/>
+      <x:c r="B3" s="3"/>
+      <x:c r="C3" s="3"/>
+      <x:c r="D3" s="3"/>
+      <x:c r="E3" s="3"/>
+      <x:c r="F3" s="3"/>
+      <x:c r="G3" s="3"/>
+    </x:row>
+    <x:row r="4" ht="34" customHeight="1">
+      <x:c r="A4" s="10" t="str">
+        <x:v>扰动</x:v>
+      </x:c>
+      <x:c r="B4" s="10" t="str">
+        <x:v>倍率</x:v>
+      </x:c>
+      <x:c r="C4" s="10" t="str">
+        <x:v>归一化权重</x:v>
+      </x:c>
+      <x:c r="D4" s="10" t="str">
+        <x:v>接收率变化</x:v>
+      </x:c>
+      <x:c r="E4" s="10" t="str">
+        <x:v>成功率变化</x:v>
+      </x:c>
+      <x:c r="F4" s="10" t="str">
+        <x:v>MEC均值变化(m)</x:v>
+      </x:c>
+      <x:c r="G4" s="10" t="str">
+        <x:v>时间均值变化(s)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="13" t="str">
+        <x:v>w1几何</x:v>
+      </x:c>
+      <x:c r="B5" s="13" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="str">
+        <x:v>0.000;0.250;0.500;0.250</x:v>
+      </x:c>
+      <x:c r="D5" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E5" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F5" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G5" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="13" t="str">
+        <x:v>w1几何</x:v>
+      </x:c>
+      <x:c r="B6" s="13" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="C6" s="13" t="str">
+        <x:v>0.000;0.250;0.500;0.250</x:v>
+      </x:c>
+      <x:c r="D6" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E6" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F6" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G6" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="13" t="str">
+        <x:v>w2接收</x:v>
+      </x:c>
+      <x:c r="B7" s="13" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="C7" s="13" t="str">
+        <x:v>0.000;0.231;0.513;0.256</x:v>
+      </x:c>
+      <x:c r="D7" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E7" s="13" t="n">
+        <x:v>-0.04999999999999999</x:v>
+      </x:c>
+      <x:c r="F7" s="13" t="n">
+        <x:v>-0.9207352296470006</x:v>
+      </x:c>
+      <x:c r="G7" s="13" t="n">
+        <x:v>1.6454606566185248e-9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="13" t="str">
+        <x:v>w2接收</x:v>
+      </x:c>
+      <x:c r="B8" s="13" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="C8" s="13" t="str">
+        <x:v>0.000;0.268;0.488;0.244</x:v>
+      </x:c>
+      <x:c r="D8" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E8" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F8" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G8" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="13" t="str">
+        <x:v>w3时间</x:v>
+      </x:c>
+      <x:c r="B9" s="13" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="C9" s="13" t="str">
+        <x:v>0.000;0.263;0.474;0.263</x:v>
+      </x:c>
+      <x:c r="D9" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E9" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F9" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="13" t="str">
+        <x:v>w3时间</x:v>
+      </x:c>
+      <x:c r="B10" s="13" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="C10" s="13" t="str">
+        <x:v>0.000;0.238;0.524;0.238</x:v>
+      </x:c>
+      <x:c r="D10" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E10" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F10" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G10" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="13" t="str">
+        <x:v>w4预测</x:v>
+      </x:c>
+      <x:c r="B11" s="13" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="C11" s="13" t="str">
+        <x:v>0.000;0.256;0.513;0.231</x:v>
+      </x:c>
+      <x:c r="D11" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E11" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F11" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G11" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="13" t="str">
+        <x:v>w4预测</x:v>
+      </x:c>
+      <x:c r="B12" s="13" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="C12" s="13" t="str">
+        <x:v>0.000;0.244;0.488;0.268</x:v>
+      </x:c>
+      <x:c r="D12" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E12" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F12" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G12" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04a96e2cedaf4314"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1323,7 +1627,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90deec051ccd45a8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re66b07285d784ece"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1481,7 +1785,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1774bd589d6f4a83"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa3680ebe5d14bc4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1731,7 +2035,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc00a1ebbe97846f4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1535fac7777646d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1812,7 +2116,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2aadbc4830054569"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a0a23a21cc0470a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1905,7 +2209,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5583fd94cb84d21"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62133f6a74494b11"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2029,7 +2333,1603 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R861ef99d14704f45"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra73ac02b96634783"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF7F9DB9"/>
+  </x:sheetPr>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="13" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="13" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="13.600000381469727" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14.800000190734863" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="13" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="13.600000381469727" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="14.800000190734863" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>问题2 第二检测点实验</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="4" t="str">
+        <x:v>20个训练场景、35组权重的外层蒙特卡洛网格校准</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="3"/>
+      <x:c r="B3" s="3"/>
+      <x:c r="C3" s="3"/>
+      <x:c r="D3" s="3"/>
+      <x:c r="E3" s="3"/>
+      <x:c r="F3" s="3"/>
+      <x:c r="G3" s="3"/>
+      <x:c r="H3" s="3"/>
+      <x:c r="I3" s="3"/>
+      <x:c r="J3" s="3"/>
+      <x:c r="K3" s="3"/>
+      <x:c r="L3" s="3"/>
+    </x:row>
+    <x:row r="4" ht="34" customHeight="1">
+      <x:c r="A4" s="10" t="str">
+        <x:v>权重w1几何</x:v>
+      </x:c>
+      <x:c r="B4" s="10" t="str">
+        <x:v>权重w2接收</x:v>
+      </x:c>
+      <x:c r="C4" s="10" t="str">
+        <x:v>权重w3时间</x:v>
+      </x:c>
+      <x:c r="D4" s="10" t="str">
+        <x:v>权重w4预测</x:v>
+      </x:c>
+      <x:c r="E4" s="10" t="str">
+        <x:v>外层损失L</x:v>
+      </x:c>
+      <x:c r="F4" s="10" t="str">
+        <x:v>接收率</x:v>
+      </x:c>
+      <x:c r="G4" s="10" t="str">
+        <x:v>MEC均值(m)</x:v>
+      </x:c>
+      <x:c r="H4" s="10" t="str">
+        <x:v>MEC中位数(m)</x:v>
+      </x:c>
+      <x:c r="I4" s="10" t="str">
+        <x:v>MEC_P90(m)</x:v>
+      </x:c>
+      <x:c r="J4" s="10" t="str">
+        <x:v>≤20m成功率</x:v>
+      </x:c>
+      <x:c r="K4" s="10" t="str">
+        <x:v>总时间均值(s)</x:v>
+      </x:c>
+      <x:c r="L4" s="10" t="str">
+        <x:v>总时间P90(s)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B5" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="D5" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="E5" s="13" t="n">
+        <x:v>2.4375382653815985</x:v>
+      </x:c>
+      <x:c r="F5" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G5" s="13" t="n">
+        <x:v>46.04357990754808</x:v>
+      </x:c>
+      <x:c r="H5" s="13" t="n">
+        <x:v>37.234757107179014</x:v>
+      </x:c>
+      <x:c r="I5" s="13" t="n">
+        <x:v>83.18448901434937</x:v>
+      </x:c>
+      <x:c r="J5" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="K5" s="13" t="n">
+        <x:v>91.00000000168757</x:v>
+      </x:c>
+      <x:c r="L5" s="13" t="n">
+        <x:v>125.0000000049733</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B6" s="13" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="C6" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="D6" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="E6" s="13" t="n">
+        <x:v>2.4375382653815985</x:v>
+      </x:c>
+      <x:c r="F6" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G6" s="13" t="n">
+        <x:v>46.04357990754808</x:v>
+      </x:c>
+      <x:c r="H6" s="13" t="n">
+        <x:v>37.234757107179014</x:v>
+      </x:c>
+      <x:c r="I6" s="13" t="n">
+        <x:v>83.18448901434937</x:v>
+      </x:c>
+      <x:c r="J6" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="K6" s="13" t="n">
+        <x:v>91.00000000168757</x:v>
+      </x:c>
+      <x:c r="L6" s="13" t="n">
+        <x:v>125.0000000049733</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="B7" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="C7" s="13" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="D7" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E7" s="13" t="n">
+        <x:v>2.5119438934099696</x:v>
+      </x:c>
+      <x:c r="F7" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G7" s="13" t="n">
+        <x:v>38.09719463713538</x:v>
+      </x:c>
+      <x:c r="H7" s="13" t="n">
+        <x:v>29.579243153932808</x:v>
+      </x:c>
+      <x:c r="I7" s="13" t="n">
+        <x:v>83.18448901434937</x:v>
+      </x:c>
+      <x:c r="J7" s="13" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="K7" s="13" t="n">
+        <x:v>105.0000000029388</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="n">
+        <x:v>125.0000000049733</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="B8" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C8" s="13" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="D8" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="E8" s="13" t="n">
+        <x:v>2.7239414897769496</x:v>
+      </x:c>
+      <x:c r="F8" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G8" s="13" t="n">
+        <x:v>32.030407783711325</x:v>
+      </x:c>
+      <x:c r="H8" s="13" t="n">
+        <x:v>34.809869827156604</x:v>
+      </x:c>
+      <x:c r="I8" s="13" t="n">
+        <x:v>57.27677003194078</x:v>
+      </x:c>
+      <x:c r="J8" s="13" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>125.00000000200039</x:v>
+      </x:c>
+      <x:c r="L8" s="13" t="n">
+        <x:v>125.00000000562659</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B9" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="C9" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="D9" s="13" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="E9" s="13" t="n">
+        <x:v>2.7258405778663692</x:v>
+      </x:c>
+      <x:c r="F9" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G9" s="13" t="n">
+        <x:v>27.125362185324217</x:v>
+      </x:c>
+      <x:c r="H9" s="13" t="n">
+        <x:v>20.452203171958942</x:v>
+      </x:c>
+      <x:c r="I9" s="13" t="n">
+        <x:v>44.645274976555214</x:v>
+      </x:c>
+      <x:c r="J9" s="13" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="K9" s="13" t="n">
+        <x:v>131.00000000331028</x:v>
+      </x:c>
+      <x:c r="L9" s="13" t="n">
+        <x:v>165.00000000672088</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B10" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C10" s="13" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="D10" s="13" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="E10" s="13" t="n">
+        <x:v>3.0671288476532057</x:v>
+      </x:c>
+      <x:c r="F10" s="13" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="G10" s="13" t="n">
+        <x:v>80.77310902393714</x:v>
+      </x:c>
+      <x:c r="H10" s="13" t="n">
+        <x:v>63.39277981982422</x:v>
+      </x:c>
+      <x:c r="I10" s="13" t="n">
+        <x:v>110.76117305423479</x:v>
+      </x:c>
+      <x:c r="J10" s="13" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="K10" s="13" t="n">
+        <x:v>85.00000000043696</x:v>
+      </x:c>
+      <x:c r="L10" s="13" t="n">
+        <x:v>85.00000000690666</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B11" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C11" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="D11" s="13" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="E11" s="13" t="n">
+        <x:v>3.100026757522434</x:v>
+      </x:c>
+      <x:c r="F11" s="13" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="G11" s="13" t="n">
+        <x:v>65.7513378459684</x:v>
+      </x:c>
+      <x:c r="H11" s="13" t="n">
+        <x:v>49.34678292143104</x:v>
+      </x:c>
+      <x:c r="I11" s="13" t="n">
+        <x:v>85.4160232633546</x:v>
+      </x:c>
+      <x:c r="J11" s="13" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="K11" s="13" t="n">
+        <x:v>104.99999999908705</x:v>
+      </x:c>
+      <x:c r="L11" s="13" t="n">
+        <x:v>105.00000000493702</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="B12" s="13" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="C12" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="D12" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E12" s="13" t="n">
+        <x:v>3.2834987542826775</x:v>
+      </x:c>
+      <x:c r="F12" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G12" s="13" t="n">
+        <x:v>21.674937661024096</x:v>
+      </x:c>
+      <x:c r="H12" s="13" t="n">
+        <x:v>18.85479794850169</x:v>
+      </x:c>
+      <x:c r="I12" s="13" t="n">
+        <x:v>31.57984703274055</x:v>
+      </x:c>
+      <x:c r="J12" s="13" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="K12" s="13" t="n">
+        <x:v>171.00000000331676</x:v>
+      </x:c>
+      <x:c r="L12" s="13" t="n">
+        <x:v>205.00000000721215</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="13" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="B13" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C13" s="13" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="D13" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E13" s="13" t="n">
+        <x:v>3.3267512677354656</x:v>
+      </x:c>
+      <x:c r="F13" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G13" s="13" t="n">
+        <x:v>23.837563334946964</x:v>
+      </x:c>
+      <x:c r="H13" s="13" t="n">
+        <x:v>21.26572882011483</x:v>
+      </x:c>
+      <x:c r="I13" s="13" t="n">
+        <x:v>34.63280012715132</x:v>
+      </x:c>
+      <x:c r="J13" s="13" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="K13" s="13" t="n">
+        <x:v>171.00000000177664</x:v>
+      </x:c>
+      <x:c r="L13" s="13" t="n">
+        <x:v>205.00000000473796</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="B14" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="C14" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="D14" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="E14" s="13" t="n">
+        <x:v>3.3882599465055017</x:v>
+      </x:c>
+      <x:c r="F14" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G14" s="13" t="n">
+        <x:v>21.07966393645844</x:v>
+      </x:c>
+      <x:c r="H14" s="13" t="n">
+        <x:v>18.433518986326824</x:v>
+      </x:c>
+      <x:c r="I14" s="13" t="n">
+        <x:v>31.57984703274055</x:v>
+      </x:c>
+      <x:c r="J14" s="13" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="K14" s="13" t="n">
+        <x:v>178.0000000036919</x:v>
+      </x:c>
+      <x:c r="L14" s="13" t="n">
+        <x:v>205.00000000721215</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B15" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C15" s="13" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="D15" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="E15" s="13" t="n">
+        <x:v>3.466871365036962</x:v>
+      </x:c>
+      <x:c r="F15" s="13" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="G15" s="13" t="n">
+        <x:v>134.09356823883624</x:v>
+      </x:c>
+      <x:c r="H15" s="13" t="n">
+        <x:v>123.78017289207695</x:v>
+      </x:c>
+      <x:c r="I15" s="13" t="n">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="J15" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K15" s="13" t="n">
+        <x:v>44.99999999971554</x:v>
+      </x:c>
+      <x:c r="L15" s="13" t="n">
+        <x:v>45.00000000482426</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B16" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="C16" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D16" s="13" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="E16" s="13" t="n">
+        <x:v>3.777435132012195</x:v>
+      </x:c>
+      <x:c r="F16" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G16" s="13" t="n">
+        <x:v>21.371756539530463</x:v>
+      </x:c>
+      <x:c r="H16" s="13" t="n">
+        <x:v>21.183992644864098</x:v>
+      </x:c>
+      <x:c r="I16" s="13" t="n">
+        <x:v>27.959687880736336</x:v>
+      </x:c>
+      <x:c r="J16" s="13" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="K16" s="13" t="n">
+        <x:v>201.00000000228107</x:v>
+      </x:c>
+      <x:c r="L16" s="13" t="n">
+        <x:v>225.00000000816777</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B17" s="13" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="C17" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D17" s="13" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="E17" s="13" t="n">
+        <x:v>3.777435132012195</x:v>
+      </x:c>
+      <x:c r="F17" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G17" s="13" t="n">
+        <x:v>21.371756539530463</x:v>
+      </x:c>
+      <x:c r="H17" s="13" t="n">
+        <x:v>21.183992644864098</x:v>
+      </x:c>
+      <x:c r="I17" s="13" t="n">
+        <x:v>27.959687880736336</x:v>
+      </x:c>
+      <x:c r="J17" s="13" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="K17" s="13" t="n">
+        <x:v>201.00000000228107</x:v>
+      </x:c>
+      <x:c r="L17" s="13" t="n">
+        <x:v>225.00000000816777</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B18" s="13" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="C18" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D18" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="E18" s="13" t="n">
+        <x:v>3.777435132012195</x:v>
+      </x:c>
+      <x:c r="F18" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G18" s="13" t="n">
+        <x:v>21.371756539530463</x:v>
+      </x:c>
+      <x:c r="H18" s="13" t="n">
+        <x:v>21.183992644864098</x:v>
+      </x:c>
+      <x:c r="I18" s="13" t="n">
+        <x:v>27.959687880736336</x:v>
+      </x:c>
+      <x:c r="J18" s="13" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="K18" s="13" t="n">
+        <x:v>201.00000000228107</x:v>
+      </x:c>
+      <x:c r="L18" s="13" t="n">
+        <x:v>225.00000000816777</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="13" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="B19" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="C19" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="D19" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E19" s="13" t="n">
+        <x:v>3.943685235209616</x:v>
+      </x:c>
+      <x:c r="F19" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G19" s="13" t="n">
+        <x:v>21.350928364327743</x:v>
+      </x:c>
+      <x:c r="H19" s="13" t="n">
+        <x:v>21.043062053828965</x:v>
+      </x:c>
+      <x:c r="I19" s="13" t="n">
+        <x:v>26.230036956069256</x:v>
+      </x:c>
+      <x:c r="J19" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="K19" s="13" t="n">
+        <x:v>211.00000000083656</x:v>
+      </x:c>
+      <x:c r="L19" s="13" t="n">
+        <x:v>245.00000000254332</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="B20" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="C20" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D20" s="13" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="E20" s="13" t="n">
+        <x:v>3.9563030610520515</x:v>
+      </x:c>
+      <x:c r="F20" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G20" s="13" t="n">
+        <x:v>21.981819656915366</x:v>
+      </x:c>
+      <x:c r="H20" s="13" t="n">
+        <x:v>22.294781940019618</x:v>
+      </x:c>
+      <x:c r="I20" s="13" t="n">
+        <x:v>26.768085661950757</x:v>
+      </x:c>
+      <x:c r="J20" s="13" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="K20" s="13" t="n">
+        <x:v>211.00000000027754</x:v>
+      </x:c>
+      <x:c r="L20" s="13" t="n">
+        <x:v>245.00000000005411</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="B21" s="13" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="C21" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D21" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="E21" s="13" t="n">
+        <x:v>3.9563030610520515</x:v>
+      </x:c>
+      <x:c r="F21" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G21" s="13" t="n">
+        <x:v>21.981819656915366</x:v>
+      </x:c>
+      <x:c r="H21" s="13" t="n">
+        <x:v>22.294781940019618</x:v>
+      </x:c>
+      <x:c r="I21" s="13" t="n">
+        <x:v>26.768085661950757</x:v>
+      </x:c>
+      <x:c r="J21" s="13" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="K21" s="13" t="n">
+        <x:v>211.00000000027754</x:v>
+      </x:c>
+      <x:c r="L21" s="13" t="n">
+        <x:v>245.00000000005411</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="13" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="B22" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="C22" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D22" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="E22" s="13" t="n">
+        <x:v>4.068788725332148</x:v>
+      </x:c>
+      <x:c r="F22" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G22" s="13" t="n">
+        <x:v>21.772769536892945</x:v>
+      </x:c>
+      <x:c r="H22" s="13" t="n">
+        <x:v>22.294781940019618</x:v>
+      </x:c>
+      <x:c r="I22" s="13" t="n">
+        <x:v>26.768085661950757</x:v>
+      </x:c>
+      <x:c r="J22" s="13" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="K22" s="13" t="n">
+        <x:v>217.99999999863707</x:v>
+      </x:c>
+      <x:c r="L22" s="13" t="n">
+        <x:v>245.00000000005411</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="B23" s="13" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="C23" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D23" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E23" s="13" t="n">
+        <x:v>4.0751627272011195</x:v>
+      </x:c>
+      <x:c r="F23" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G23" s="13" t="n">
+        <x:v>22.09146963007419</x:v>
+      </x:c>
+      <x:c r="H23" s="13" t="n">
+        <x:v>22.294781940019618</x:v>
+      </x:c>
+      <x:c r="I23" s="13" t="n">
+        <x:v>26.768085661950757</x:v>
+      </x:c>
+      <x:c r="J23" s="13" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="K23" s="13" t="n">
+        <x:v>217.9999999989579</x:v>
+      </x:c>
+      <x:c r="L23" s="13" t="n">
+        <x:v>245.00000000005411</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="B24" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C24" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="D24" s="13" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="E24" s="13" t="n">
+        <x:v>4.075620433233621</x:v>
+      </x:c>
+      <x:c r="F24" s="13" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="G24" s="13" t="n">
+        <x:v>48.69768827498034</x:v>
+      </x:c>
+      <x:c r="H24" s="13" t="n">
+        <x:v>30.90299420436569</x:v>
+      </x:c>
+      <x:c r="I24" s="13" t="n">
+        <x:v>49.08359726419898</x:v>
+      </x:c>
+      <x:c r="J24" s="13" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="K24" s="13" t="n">
+        <x:v>183.99999999903295</x:v>
+      </x:c>
+      <x:c r="L24" s="13" t="n">
+        <x:v>205.00000000188592</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="13" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="B25" s="13" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="C25" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D25" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E25" s="13" t="n">
+        <x:v>4.113282740304054</x:v>
+      </x:c>
+      <x:c r="F25" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G25" s="13" t="n">
+        <x:v>21.497470283922894</x:v>
+      </x:c>
+      <x:c r="H25" s="13" t="n">
+        <x:v>21.043062053828965</x:v>
+      </x:c>
+      <x:c r="I25" s="13" t="n">
+        <x:v>26.230036956069256</x:v>
+      </x:c>
+      <x:c r="J25" s="13" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="K25" s="13" t="n">
+        <x:v>220.9999999994556</x:v>
+      </x:c>
+      <x:c r="L25" s="13" t="n">
+        <x:v>245.00000000254332</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B26" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C26" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D26" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E26" s="13" t="n">
+        <x:v>4.198918799518739</x:v>
+      </x:c>
+      <x:c r="F26" s="13" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="G26" s="13" t="n">
+        <x:v>49.0292732540422</x:v>
+      </x:c>
+      <x:c r="H26" s="13" t="n">
+        <x:v>28.6858763064473</x:v>
+      </x:c>
+      <x:c r="I26" s="13" t="n">
+        <x:v>46.52842832082102</x:v>
+      </x:c>
+      <x:c r="J26" s="13" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K26" s="13" t="n">
+        <x:v>190.99999999879265</x:v>
+      </x:c>
+      <x:c r="L26" s="13" t="n">
+        <x:v>205.00000000188592</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="13" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="B27" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C27" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="D27" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E27" s="13" t="n">
+        <x:v>4.206953791058803</x:v>
+      </x:c>
+      <x:c r="F27" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G27" s="13" t="n">
+        <x:v>22.847689487816872</x:v>
+      </x:c>
+      <x:c r="H27" s="13" t="n">
+        <x:v>21.709913492699336</x:v>
+      </x:c>
+      <x:c r="I27" s="13" t="n">
+        <x:v>29.459771981660683</x:v>
+      </x:c>
+      <x:c r="J27" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="K27" s="13" t="n">
+        <x:v>224.99999999865454</x:v>
+      </x:c>
+      <x:c r="L27" s="13" t="n">
+        <x:v>245.00000000254332</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="13" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="B28" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C28" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="D28" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="E28" s="13" t="n">
+        <x:v>4.373028497604074</x:v>
+      </x:c>
+      <x:c r="F28" s="13" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="G28" s="13" t="n">
+        <x:v>36.109758152061524</x:v>
+      </x:c>
+      <x:c r="H28" s="13" t="n">
+        <x:v>24.583298591082638</x:v>
+      </x:c>
+      <x:c r="I28" s="13" t="n">
+        <x:v>38.01005748976844</x:v>
+      </x:c>
+      <x:c r="J28" s="13" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="K28" s="13" t="n">
+        <x:v>217.99999999675038</x:v>
+      </x:c>
+      <x:c r="L28" s="13" t="n">
+        <x:v>225.00000000019514</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="13" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="B29" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="C29" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D29" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E29" s="13" t="n">
+        <x:v>4.426400251961288</x:v>
+      </x:c>
+      <x:c r="F29" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G29" s="13" t="n">
+        <x:v>22.98667919484384</x:v>
+      </x:c>
+      <x:c r="H29" s="13" t="n">
+        <x:v>23.214026064907273</x:v>
+      </x:c>
+      <x:c r="I29" s="13" t="n">
+        <x:v>27.587618679546253</x:v>
+      </x:c>
+      <x:c r="J29" s="13" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="K29" s="13" t="n">
+        <x:v>237.9999999997784</x:v>
+      </x:c>
+      <x:c r="L29" s="13" t="n">
+        <x:v>265.00000000491883</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="B30" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C30" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D30" s="13" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="E30" s="13" t="n">
+        <x:v>4.50501494849305</x:v>
+      </x:c>
+      <x:c r="F30" s="13" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="G30" s="13" t="n">
+        <x:v>36.87574736058696</x:v>
+      </x:c>
+      <x:c r="H30" s="13" t="n">
+        <x:v>24.583298591082638</x:v>
+      </x:c>
+      <x:c r="I30" s="13" t="n">
+        <x:v>38.810562870326216</x:v>
+      </x:c>
+      <x:c r="J30" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="K30" s="13" t="n">
+        <x:v>224.9999999973853</x:v>
+      </x:c>
+      <x:c r="L30" s="13" t="n">
+        <x:v>225.00000000371847</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B31" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C31" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D31" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E31" s="13" t="n">
+        <x:v>4.60968885606781</x:v>
+      </x:c>
+      <x:c r="F31" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G31" s="13" t="n">
+        <x:v>23.817776064308312</x:v>
+      </x:c>
+      <x:c r="H31" s="13" t="n">
+        <x:v>23.31253693594849</x:v>
+      </x:c>
+      <x:c r="I31" s="13" t="n">
+        <x:v>27.587618679546253</x:v>
+      </x:c>
+      <x:c r="J31" s="13" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="K31" s="13" t="n">
+        <x:v>247.99999999927928</x:v>
+      </x:c>
+      <x:c r="L31" s="13" t="n">
+        <x:v>265.00000000491883</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="13" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="B32" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C32" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D32" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="E32" s="13" t="n">
+        <x:v>4.618525866715511</x:v>
+      </x:c>
+      <x:c r="F32" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G32" s="13" t="n">
+        <x:v>24.259626595855153</x:v>
+      </x:c>
+      <x:c r="H32" s="13" t="n">
+        <x:v>23.67934916656218</x:v>
+      </x:c>
+      <x:c r="I32" s="13" t="n">
+        <x:v>27.587618679546253</x:v>
+      </x:c>
+      <x:c r="J32" s="13" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="K32" s="13" t="n">
+        <x:v>248.00000000028513</x:v>
+      </x:c>
+      <x:c r="L32" s="13" t="n">
+        <x:v>265.00000000491883</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="13" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="B33" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C33" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D33" s="13" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="E33" s="13" t="n">
+        <x:v>4.644491442019522</x:v>
+      </x:c>
+      <x:c r="F33" s="13" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="G33" s="13" t="n">
+        <x:v>35.51623870052613</x:v>
+      </x:c>
+      <x:c r="H33" s="13" t="n">
+        <x:v>23.695387298338925</x:v>
+      </x:c>
+      <x:c r="I33" s="13" t="n">
+        <x:v>30.15484950827206</x:v>
+      </x:c>
+      <x:c r="J33" s="13" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="K33" s="13" t="n">
+        <x:v>234.99999999751353</x:v>
+      </x:c>
+      <x:c r="L33" s="13" t="n">
+        <x:v>245.00000000005411</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B34" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C34" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D34" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E34" s="13" t="n">
+        <x:v>5.210926121990785</x:v>
+      </x:c>
+      <x:c r="F34" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G34" s="13" t="n">
+        <x:v>206.79630608081487</x:v>
+      </x:c>
+      <x:c r="H34" s="13" t="n">
+        <x:v>208.6483445407723</x:v>
+      </x:c>
+      <x:c r="I34" s="13" t="n">
+        <x:v>425.6869073786244</x:v>
+      </x:c>
+      <x:c r="J34" s="13" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="K34" s="13" t="n">
+        <x:v>64.49999999968112</x:v>
+      </x:c>
+      <x:c r="L34" s="13" t="n">
+        <x:v>105.00000000510417</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B35" s="13" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="C35" s="13" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="D35" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E35" s="13" t="n">
+        <x:v>5.539366636304514</x:v>
+      </x:c>
+      <x:c r="F35" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G35" s="13" t="n">
+        <x:v>223.21833179730356</x:v>
+      </x:c>
+      <x:c r="H35" s="13" t="n">
+        <x:v>221.802110848734</x:v>
+      </x:c>
+      <x:c r="I35" s="13" t="n">
+        <x:v>420.36399304630584</x:v>
+      </x:c>
+      <x:c r="J35" s="13" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="K35" s="13" t="n">
+        <x:v>64.49999999871844</x:v>
+      </x:c>
+      <x:c r="L35" s="13" t="n">
+        <x:v>105.00000000510417</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B36" s="13" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="C36" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="D36" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E36" s="13" t="n">
+        <x:v>5.539366636304514</x:v>
+      </x:c>
+      <x:c r="F36" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G36" s="13" t="n">
+        <x:v>223.21833179730356</x:v>
+      </x:c>
+      <x:c r="H36" s="13" t="n">
+        <x:v>221.802110848734</x:v>
+      </x:c>
+      <x:c r="I36" s="13" t="n">
+        <x:v>420.36399304630584</x:v>
+      </x:c>
+      <x:c r="J36" s="13" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="K36" s="13" t="n">
+        <x:v>64.49999999871844</x:v>
+      </x:c>
+      <x:c r="L36" s="13" t="n">
+        <x:v>105.00000000510417</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="B37" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C37" s="13" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="D37" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E37" s="13" t="n">
+        <x:v>6.331277412308696</x:v>
+      </x:c>
+      <x:c r="F37" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G37" s="13" t="n">
+        <x:v>304.0638706087352</x:v>
+      </x:c>
+      <x:c r="H37" s="13" t="n">
+        <x:v>343.0407365757244</x:v>
+      </x:c>
+      <x:c r="I37" s="13" t="n">
+        <x:v>479.99144316011785</x:v>
+      </x:c>
+      <x:c r="J37" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K37" s="13" t="n">
+        <x:v>15.000000002739881</x:v>
+      </x:c>
+      <x:c r="L37" s="13" t="n">
+        <x:v>15.000000006563422</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B38" s="13" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="C38" s="13" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="D38" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E38" s="13" t="n">
+        <x:v>7.812228468597115</x:v>
+      </x:c>
+      <x:c r="F38" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G38" s="13" t="n">
+        <x:v>374.3614234279185</x:v>
+      </x:c>
+      <x:c r="H38" s="13" t="n">
+        <x:v>385.6333351128699</x:v>
+      </x:c>
+      <x:c r="I38" s="13" t="n">
+        <x:v>533.2122456303864</x:v>
+      </x:c>
+      <x:c r="J38" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K38" s="13" t="n">
+        <x:v>19.499999995435243</x:v>
+      </x:c>
+      <x:c r="L38" s="13" t="n">
+        <x:v>44.999999994741586</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B39" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C39" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D39" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E39" s="13" t="n">
+        <x:v>9.460554908638763</x:v>
+      </x:c>
+      <x:c r="F39" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G39" s="13" t="n">
+        <x:v>460.5277454331226</x:v>
+      </x:c>
+      <x:c r="H39" s="13" t="n">
+        <x:v>500.83144743253115</x:v>
+      </x:c>
+      <x:c r="I39" s="13" t="n">
+        <x:v>637.3132695996346</x:v>
+      </x:c>
+      <x:c r="J39" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K39" s="13" t="n">
+        <x:v>14.99999999327898</x:v>
+      </x:c>
+      <x:c r="L39" s="13" t="n">
+        <x:v>14.999999996120453</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf84c6e80a2744a67"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF7F9DB9"/>
+  </x:sheetPr>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13.600000381469727" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14.800000190734863" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="13" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="13.600000381469727" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14.800000190734863" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>问题2 第二检测点实验</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="4" t="str">
+        <x:v>40个独立场景的实际二测回放结果</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="3"/>
+      <x:c r="B3" s="3"/>
+      <x:c r="C3" s="3"/>
+      <x:c r="D3" s="3"/>
+      <x:c r="E3" s="3"/>
+      <x:c r="F3" s="3"/>
+      <x:c r="G3" s="3"/>
+      <x:c r="H3" s="3"/>
+    </x:row>
+    <x:row r="4" ht="34" customHeight="1">
+      <x:c r="A4" s="10" t="str">
+        <x:v>策略</x:v>
+      </x:c>
+      <x:c r="B4" s="10" t="str">
+        <x:v>接收率</x:v>
+      </x:c>
+      <x:c r="C4" s="10" t="str">
+        <x:v>MEC均值(m)</x:v>
+      </x:c>
+      <x:c r="D4" s="10" t="str">
+        <x:v>MEC中位数(m)</x:v>
+      </x:c>
+      <x:c r="E4" s="10" t="str">
+        <x:v>MEC_P90(m)</x:v>
+      </x:c>
+      <x:c r="F4" s="10" t="str">
+        <x:v>≤20m成功率</x:v>
+      </x:c>
+      <x:c r="G4" s="10" t="str">
+        <x:v>总时间均值(s)</x:v>
+      </x:c>
+      <x:c r="H4" s="10" t="str">
+        <x:v>总时间P90(s)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="13" t="str">
+        <x:v>四指标联合</x:v>
+      </x:c>
+      <x:c r="B5" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="n">
+        <x:v>42.61635830518835</x:v>
+      </x:c>
+      <x:c r="D5" s="13" t="n">
+        <x:v>38.94547069789232</x:v>
+      </x:c>
+      <x:c r="E5" s="13" t="n">
+        <x:v>82.92928509571875</x:v>
+      </x:c>
+      <x:c r="F5" s="13" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="G5" s="13" t="n">
+        <x:v>109.00000000248482</x:v>
+      </x:c>
+      <x:c r="H5" s="13" t="n">
+        <x:v>125.00000000720448</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="13" t="str">
+        <x:v>仅几何</x:v>
+      </x:c>
+      <x:c r="B6" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C6" s="13" t="n">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D6" s="13" t="n">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="E6" s="13" t="n">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="F6" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G6" s="13" t="n">
+        <x:v>361.0000000019596</x:v>
+      </x:c>
+      <x:c r="H6" s="13" t="n">
+        <x:v>365.0000000078777</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="13" t="str">
+        <x:v>最近点</x:v>
+      </x:c>
+      <x:c r="B7" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="13" t="n">
+        <x:v>437.65887171482746</x:v>
+      </x:c>
+      <x:c r="D7" s="13" t="n">
+        <x:v>484.25562039901655</x:v>
+      </x:c>
+      <x:c r="E7" s="13" t="n">
+        <x:v>599.6046380317338</x:v>
+      </x:c>
+      <x:c r="F7" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G7" s="13" t="n">
+        <x:v>14.999999993846483</x:v>
+      </x:c>
+      <x:c r="H7" s="13" t="n">
+        <x:v>14.999999998419991</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="13" t="str">
+        <x:v>随机点</x:v>
+      </x:c>
+      <x:c r="B8" s="13" t="n">
+        <x:v>0.675</x:v>
+      </x:c>
+      <x:c r="C8" s="13" t="n">
+        <x:v>187.04157206740314</x:v>
+      </x:c>
+      <x:c r="D8" s="13" t="n">
+        <x:v>198.70641623116492</x:v>
+      </x:c>
+      <x:c r="E8" s="13" t="n">
+        <x:v>350.68506280300744</x:v>
+      </x:c>
+      <x:c r="F8" s="13" t="n">
+        <x:v>0.025</x:v>
+      </x:c>
+      <x:c r="G8" s="13" t="n">
+        <x:v>181.00000000099396</x:v>
+      </x:c>
+      <x:c r="H8" s="13" t="n">
+        <x:v>305.0000000074258</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46a81337ce5a49a8"/>
   </x:tableParts>
 </x:worksheet>
 </file>